--- a/demo_output/test/prompt_1/figure_03_EU vs. USA naturgas — prisforskel (USD-MWh).xlsx
+++ b/demo_output/test/prompt_1/figure_03_EU vs. USA naturgas — prisforskel (USD-MWh).xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grafik" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TTF naturgas (EU)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TTF naturgas (Europa)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Henry Hub naturgas (USA)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>TTF naturgas (EU)</t>
+          <t>TTF naturgas (Europa)</t>
         </is>
       </c>
     </row>

--- a/demo_output/test/prompt_1/figure_03_EU vs. USA naturgas — prisforskel (USD-MWh).xlsx
+++ b/demo_output/test/prompt_1/figure_03_EU vs. USA naturgas — prisforskel (USD-MWh).xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grafik" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TTF naturgas (Europa)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TTF naturgas (EU)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Henry Hub naturgas (USA)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>TTF naturgas (Europa)</t>
+          <t>TTF naturgas (EU)</t>
         </is>
       </c>
     </row>
